--- a/engenharia/terraplanagem-u6310/MC-TERRAPLANAGEM_U-6310_U-6312_Rev0.xlsx
+++ b/engenharia/terraplanagem-u6310/MC-TERRAPLANAGEM_U-6310_U-6312_Rev0.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,8 +221,7 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1350,7 +1349,7 @@
           <t>Fator de empolamento — cenário alternativo</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="19" t="n">
         <v>1.3</v>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -1360,7 +1359,7 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>Valor usado no estudo preliminar da equipe (aba 'Planilha1', célula B9). Mantido para análise de sensibilidade.</t>
+          <t>Valor usado no estudo preliminar da equipe — aba 'Planilha1', célula B9 do arquivo original IMPORTAÇÃO_TERRAPLAN_TANQUE.xlsx. Mantido para análise de sensibilidade.</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1487,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Raios cotados em DE-5400.00-6310-113-TX3-003 rev.0. Linha 818 sem cota de raio na planta — valor aferido graficamente e confirmado pelo volume (ver AFERIÇÃO).</t>
+          <t>Raios cotados em DE-5400.00-6310-113-TX3-003 rev.0. A linha 818 não tem cota de raio na planta — ver coluna 'Origem do raio'.</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1691,7 @@
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>Sem cota de raio na planta. Aferido no vetor da planta (12,77 m) e confirmado pelo volume do desenho.</t>
+          <t>Sem cota de raio na planta. Retro-calculado pelo volume do desenho (12,7818 m) e corroborado por medição independente no arquivo vetorial (12,77 m).</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3168,35 +3167,121 @@
     <row r="13">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>1. O modelo geométrico independente reproduz a coluna REATERRO do desenho com desvio total de 0,25% (menos de 0,1% em quatro das cinco linhas).</t>
+          <t>1. O modelo geométrico reproduz a coluna REATERRO do desenho com desvio total de +0,25%, e abaixo de 0,1% em três das cinco linhas (816, 817 e 818).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Isso comprova que o REATERRO do desenho corresponde exatamente ao volume escavado sob os tanques (tronco de cone, EL. 17,50 a 19,00, talude 1:1).</t>
+          <t xml:space="preserve">   Isso comprova que o REATERRO do desenho corresponde ao volume escavado sob os tanques (tronco de cone, EL. 17,50 a 19,00, talude de corte 1:1).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>2. A linha 815 apresenta o único desvio relevante (+1,91%, +47,71 m³): nos cortes D-D os espaçamentos são 24,11 / 23,89 / 24,00 m (não uniformes) e</t>
+          <t xml:space="preserve">   Ressalva de independência: o raio da linha 818 foi retro-calculado a partir do próprio volume do desenho, de modo que o desvio de 0,03% dessa linha</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   os círculos de topo são truncados pelo limite da plataforma (cotas 11,85 e 11,15 nas extremidades). Adotar o valor do desenho, a favor da segurança.</t>
+          <t xml:space="preserve">   não constitui verificação independente. A aferição é independente nas linhas 816, 817 e 824, cujos raios estão cotados na planta.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>3. A diferença CORTE − REATERRO é o corte de regularização da plataforma e da bacia de contenção — quantificado na aba QUANT-LINHA.</t>
+      <c r="B17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>2. A linha 815 é o único desvio relevante (+47,71 m³, +1,91%). Mecanismos identificados e quantificados por integração:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        truncamento dos quatro cones pelo limite sul da plataforma (cota 10,97 m do eixo, menor que o raio de topo 12,35 m) .... 23,05 m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        truncamento do cone da extremidade oeste (cota 11,85 m) ........................................................  0,46 m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        truncamento do cone da extremidade leste (cota 11,15 m) ........................................................  4,08 m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        sobreposição entre cones adjacentes (espaçamento 24,00 m, raio de topo 12,35 m) ................................  1,14 m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        soma .......................................................................................................... 28,73 m³  (60% do desvio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   O saldo de aproximadamente 19 m³ (0,76% da linha) permanece em aberto e deve ser confirmado com o projetista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Adota-se o valor do desenho por prevalência contratual do documento emitido — e não por margem de segurança: 2.492,22 m³ é o MENOR dos dois valores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>3. Inconsistência interna do projeto a esclarecer: o corte D-D cota os espaçamentos de eixo da linha 815 como 24,11 / 23,89 / 24,00 m, enquanto a planta</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   e as coordenadas PDMS do próprio corte (E=4208,387 / 4232,387 / 4256,387 / 4280,387) dão 24,000 m exatos. Não afeta o volume, porque a soma de</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   troncos de cone independentes não depende do espaçamento entre eles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>4. A diferença CORTE − REATERRO é o corte de regularização da plataforma e da bacia de contenção — quantificado na aba QUANT-LINHA.</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3712,8 +3797,8 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>Fração
-da linha</t>
+          <t>Fração da linha
+(1 ÷ nº de FTs)</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
@@ -3785,7 +3870,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="36">
-        <f>H5/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J5" s="26">
@@ -3847,7 +3932,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="36">
-        <f>H6/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J6" s="26">
@@ -3909,7 +3994,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="36">
-        <f>H7/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J7" s="26">
@@ -3971,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="36">
-        <f>H8/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J8" s="26">
@@ -4033,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="36">
-        <f>H9/2</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J9" s="26">
@@ -4095,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="36">
-        <f>H10/2</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J10" s="26">
@@ -4157,7 +4242,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="36">
-        <f>H11/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J11" s="26">
@@ -4219,7 +4304,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="36">
-        <f>H12/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J12" s="26">
@@ -4281,7 +4366,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="36">
-        <f>H13/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J13" s="26">
@@ -4343,7 +4428,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="36">
-        <f>H14/4</f>
+        <f>1/PREMISSAS!$C$19</f>
         <v/>
       </c>
       <c r="J14" s="26">
@@ -4434,6 +4519,20 @@
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>As datas programadas reproduzem a planilha de importação vigente e não foram alteradas por esta memória de cálculo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Cada linha de tanques é executada em 2 FTs, logo a fração é sempre 1/2 (PREMISSAS, item 15). Para a linha 816, por exemplo, cada FT abrange 2 dos 4 tanques;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>para o TQ-6312824, tanque único, cada FT abrange metade do serviço do mesmo tanque.</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4600,7 +4699,7 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>(TEXT(E10,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E10,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E10" s="29" t="n">
@@ -4645,7 +4744,7 @@
         </is>
       </c>
       <c r="D11" s="16">
-        <f>(TEXT(E11,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E11,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E11" s="29" t="n">
@@ -4690,7 +4789,7 @@
         </is>
       </c>
       <c r="D12" s="16">
-        <f>(TEXT(E12,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E12,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E12" s="29" t="n">
@@ -4735,7 +4834,7 @@
         </is>
       </c>
       <c r="D13" s="16">
-        <f>(TEXT(E13,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E13,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E13" s="29" t="n">
@@ -4780,7 +4879,7 @@
         </is>
       </c>
       <c r="D14" s="16">
-        <f>(TEXT(E14,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E14,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E14" s="29" t="n">
@@ -4825,7 +4924,7 @@
         </is>
       </c>
       <c r="D15" s="16">
-        <f>(TEXT(E15,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E15,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E15" s="29" t="n">
@@ -4870,7 +4969,7 @@
         </is>
       </c>
       <c r="D16" s="16">
-        <f>(TEXT(E16,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E16,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E16" s="29" t="n">
@@ -4915,7 +5014,7 @@
         </is>
       </c>
       <c r="D17" s="16">
-        <f>(TEXT(E17,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E17,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E17" s="29" t="n">
@@ -4960,7 +5059,7 @@
         </is>
       </c>
       <c r="D18" s="16">
-        <f>(TEXT(E18,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E18,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E18" s="29" t="n">
@@ -5005,7 +5104,7 @@
         </is>
       </c>
       <c r="D19" s="16">
-        <f>(TEXT(E19,"#,##0.00")&amp;"/2 × 70% × "&amp;TEXT($C$7,"0.00"))</f>
+        <f>(TEXT(E19,"#,##0.00")&amp;" ÷ "&amp;TEXT($C$5,"0")&amp;" × "&amp;TEXT($C$6,"0%")&amp;" × "&amp;TEXT($C$7,"0.00"))</f>
         <v/>
       </c>
       <c r="E19" s="29" t="n">
@@ -5085,7 +5184,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Representam de 52% a 80% do corte da linha correspondente, sem proporção constante. Provável origem: quantitativo preliminar,</t>
+          <t xml:space="preserve">   Representam de 53,4% a 80,2% do corte da linha correspondente, sem proporção constante. Provável origem: quantitativo preliminar,</t>
         </is>
       </c>
     </row>
@@ -5119,14 +5218,14 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>3) EFEITO. O total das 10 fichas fica em 10.408,89 m³ contra 24.175,07 m³ de corte empolado apurado nesta memória — 43% do escopo.</t>
+          <t>3) EFEITO. O total das 10 fichas fica em 10.408,89 m³ contra 24.175,07 m³ de corte empolado apurado nesta memória — 43,1% do escopo de corte.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Em volume geométrico a planilha cobre 60% do corte do desenho.</t>
+          <t xml:space="preserve">   O mesmo percentual vale em volume geométrico (10.408,89 ÷ 1,40 = 7.434,92 m³ contra 17.267,91 m³), já que o fator de empolamento incide nos dois lados.</t>
         </is>
       </c>
     </row>
@@ -5144,6 +5243,30 @@
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   para o Primavera, e confirmar com a Coordenação de Engenharia Civil o fator de empolamento a adotar (1,30 ou 1,40).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>5) ALCANCE DA COLUNA 'Quantidade'. Tanto na planilha vigente quanto nesta memória a quantidade da FT mede APENAS o corte (atividade 001).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   As atividades 002-TROCA DE SOLO, 003-ATERRO e 004-COMPACTAÇÃO, também declaradas na ficha, correspondem a outros 15.597,05 m³ in situ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   que não estão medidos em nenhuma coluna da planilha de importação. Convenção mantida igual à do cliente — registrada aqui para não induzir a erro.</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5220,7 +5343,7 @@
           <t>Escavação — corte total (volume geométrico)</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>'QUANT-LINHA'!D10</f>
         <v/>
       </c>
@@ -5246,7 +5369,7 @@
           <t xml:space="preserve">     Escavação / troca de solo sob os tanques</t>
         </is>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="30">
         <f>'QUANT-LINHA'!E10</f>
         <v/>
       </c>
@@ -5257,7 +5380,7 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>Tronco de cone EL. 17,50 → 19,00, raio = costado + 4,00 m, talude 1:1 (Nota 4). Aferido em 0,25% contra o desenho.</t>
+          <t>Valor da coluna REATERRO da tabela do desenho (adotado). O modelo de tronco de cone desta memória o reproduz com +0,25% — ver AFERIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5395,7 @@
           <t xml:space="preserve">     Corte de regularização da plataforma e bacia</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="30">
         <f>'QUANT-LINHA'!F10</f>
         <v/>
       </c>
@@ -5298,7 +5421,7 @@
           <t>Escavação — volume solto para transporte</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="30">
         <f>C5*PREMISSAS!$C$17</f>
         <v/>
       </c>
@@ -5324,7 +5447,7 @@
           <t xml:space="preserve">     Cenário alternativo (fator 1,30)</t>
         </is>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="30">
         <f>C5*PREMISSAS!$C$18</f>
         <v/>
       </c>
@@ -5350,7 +5473,7 @@
           <t>Bota-fora</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="30">
         <f>C5*PREMISSAS!$C$17</f>
         <v/>
       </c>
@@ -5376,7 +5499,7 @@
           <t>Rachão para reaterro das bases (volume in situ)</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="30">
         <f>'QUANT-LINHA'!E10</f>
         <v/>
       </c>
@@ -5402,7 +5525,7 @@
           <t>Reaterro e compactação com controle tecnológico</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="30">
         <f>'QUANT-LINHA'!E10</f>
         <v/>
       </c>
@@ -5429,7 +5552,7 @@
         </is>
       </c>
       <c r="C13" s="41">
-        <f>GEOMETRIA!D5+GEOMETRIA!D6+GEOMETRIA!D7+GEOMETRIA!D8+GEOMETRIA!D9</f>
+        <f>SUM(GEOMETRIA!D5:D9)</f>
         <v/>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -5454,8 +5577,9 @@
           <t>Nº de fichas de tarefa</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n">
-        <v>10</v>
+      <c r="C14" s="41">
+        <f>COUNTA('DISTRIB-FT'!A5:A14)</f>
+        <v/>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
@@ -5505,7 +5629,7 @@
           <t>Quantidade total lançada nas 10 FTs (planilha vigente)</t>
         </is>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="42">
         <f>'CONFRONTO-FT'!F20</f>
         <v/>
       </c>
@@ -5527,7 +5651,7 @@
           <t>Quantidade total apurada nesta memória de cálculo</t>
         </is>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="42">
         <f>'CONFRONTO-FT'!G20</f>
         <v/>
       </c>
@@ -5549,7 +5673,7 @@
           <t>Escopo faltante nas fichas de tarefa</t>
         </is>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="42">
         <f>'CONFRONTO-FT'!G20-'CONFRONTO-FT'!F20</f>
         <v/>
       </c>
@@ -5571,7 +5695,7 @@
           <t>Cobertura da planilha vigente</t>
         </is>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="43">
         <f>'CONFRONTO-FT'!F20/'CONFRONTO-FT'!G20</f>
         <v/>
       </c>
@@ -5624,35 +5748,70 @@
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>c) Raio da linha 818 não está cotado na planta. Adotado 12,78 m, aferido no arquivo vetorial e confirmado pelo volume do desenho (desvio 0,03%).</t>
+          <t>c) Raio da linha 818 não está cotado na planta. Adotado 12,78 m, retro-calculado a partir do volume do desenho e corroborado por medição no arquivo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>d) A tabela do desenho não distingue o volume do dique e dos mini-diques de contenção mostrados nos cortes A-A a E-E; se forem executados</t>
+          <t xml:space="preserve">   vetorial (12,77 m). Confirmar a cota com o projetista — a aferição dessa linha não é independente.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   em aterro compactado, o material e o volume correspondentes devem ser orçados à parte.</t>
+          <t>c1) Linha 815: desvio de +47,71 m³ (+1,91%) explicado em 60% por truncamento e sobreposição dos cones (ver AFERIÇÃO); saldo a confirmar com o projetista.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>e) Não há coluna de aterro na tabela do desenho. Caso parte do corte venha a ser reaproveitada em outra frente, o bota-fora do item 3 reduz</t>
+          <t>c2) Corte D-D cota os espaçamentos da linha 815 como 24,11 / 23,89 / 24,00 m, contra 24,000 m exatos na planta e nas coordenadas PDMS. A esclarecer.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
+          <t>d) A tabela do desenho não distingue o volume do dique e dos mini-diques de contenção mostrados nos cortes A-A a E-E; se forem executados</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   em aterro compactado, o material e o volume correspondentes devem ser orçados à parte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>e) Não há coluna de aterro na tabela do desenho. Caso parte do corte venha a ser reaproveitada em outra frente, o bota-fora do item 3 reduz</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">   na mesma proporção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>f) A coluna 'Quantidade' das fichas de tarefa mede apenas o corte (atividade 001). Troca de solo, aterro e compactação (itens 4 e 5 acima) não estão</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   medidos em nenhuma coluna da planilha de importação — convenção herdada do cliente, registrada aqui para não induzir a erro.</t>
         </is>
       </c>
     </row>
